--- a/第9回_Backpropagation/excel_backpropagation_demo.xlsx
+++ b/第9回_Backpropagation/excel_backpropagation_demo.xlsx
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -121,11 +121,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00D8DEE9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -157,6 +163,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +544,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Excelで体験する言語モデルのしくみ 第9回 Backpropagation</t>
         </is>
@@ -660,7 +669,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>12_TROUBLE: よくある確認点</t>
         </is>
@@ -685,7 +694,7 @@
           <t>よくある確認点</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -774,7 +783,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>13_SERIES_ROADMAP</t>
         </is>
@@ -801,8 +810,8 @@
           <t>全10回ロードマップ</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1022,7 +1031,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>01_INPUT: Backpropagationに使う入力と重み</t>
         </is>
@@ -1055,15 +1064,15 @@
           <t>第8回のLossとgradientを受けて、ズレを重みWと入力xへ戻す入口を確認します。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1083,11 +1092,11 @@
           <t>入力ベクトルxと重みW</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -1237,8 +1246,8 @@
           <t>biasと学習設定</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -1373,7 +1382,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>02_FORWARD_LOSS: 前向き計算とdLoss/dlogit</t>
         </is>
@@ -1404,14 +1413,14 @@
           <t>まず前向き計算でlogit、probability、target、Lossへの入口を作ります。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1430,10 +1439,10 @@
           <t>forward and output gradient</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
@@ -1593,7 +1602,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>03_DLOGIT: 出力側のズレを作る</t>
         </is>
@@ -1624,14 +1633,14 @@
           <t>Softmax + Cross Entropyでは、出力側のgradientを probability - target と読めます。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1650,9 +1659,9 @@
           <t>dLoss/dlogit</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -1801,7 +1810,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>04_DW_DX: 重みと入力へgradientを戻す</t>
         </is>
@@ -1832,14 +1841,14 @@
           <t>dWは入力xとdlogitの掛け算、dxは前段へ戻るgradientです。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1858,10 +1867,10 @@
           <t>dLoss/dW</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
@@ -1984,8 +1993,8 @@
           <t>dLoss/dx</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
@@ -2105,7 +2114,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>05_UPDATE_CHECK: 1ステップ更新でLossが下がる</t>
         </is>
@@ -2136,14 +2145,14 @@
           <t>Wとbiasを1ステップ更新し、正解tokenの確率が上がりLossが下がることを確認します。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -2162,11 +2171,11 @@
           <t>更新前後の比較</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -2334,9 +2343,9 @@
           <t>Loss summary</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
@@ -2448,7 +2457,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>06_CHAIN_RULE: chain ruleで前へ戻す</t>
         </is>
@@ -2479,14 +2488,14 @@
           <t>chain ruleは、後ろで出たズレを、式のつながりに沿って前へ戻す読み方です。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -2505,9 +2514,9 @@
           <t>Backpropagationの小さな流れ</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -2704,7 +2713,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>10_RUN_PYTHON: Python in Excel 実行手順</t>
         </is>
@@ -2729,7 +2738,7 @@
           <t>実行手順</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2818,7 +2827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:A91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -2830,572 +2839,575 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>11_PYTHON_CODE: Python in Excelへ貼り付けるコード</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>外部 .py ファイルと同じ内容です。Excelの入力表を xl(...) で参照します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>import pandas as pd</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>import numpy as np</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-    </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>features = ["明るさ", "くだけた表現", "過去形らしさ"]</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>x = np.array([0.60, 0.25, 0.80], dtype=float)</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>input_source_df = xl("'01_INPUT'!A6:F9", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>vocab = ["です", "ました", "ね", "よ"]</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>settings_source_df = xl("'01_INPUT'!A13:C16", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>W = np.array([</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.25, 0.50, -0.20, 0.10],</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>features = input_source_df["input_feature"].astype(str).tolist()</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.10, -0.15, 0.35, 0.20],</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>x = input_source_df["x_value"].astype(float).to_numpy()</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [-0.30, 0.60, 0.05, -0.10],</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>weight_columns = [c for c in input_source_df.columns if str(c).startswith("W_to_")]</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>], dtype=float)</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>vocab = [str(c).replace("W_to_", "") for c in weight_columns]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>b = np.array([0.10, 0.00, -0.05, 0.08], dtype=float)</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W = input_source_df[weight_columns].astype(float).to_numpy()</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>target_token = "ました"</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>settings = dict(zip(settings_source_df["parameter"].astype(str), settings_source_df["value"]))</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>learning_rate = 0.7</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>b = np.array([float(v.strip()) for v in str(settings.get("bias", "[0.1, 0.0, -0.05, 0.08]")).strip("[]").split(",")], dtype=float)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>target_token = str(settings.get("target_token", "ました"))</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>learning_rate = float(settings.get("learning_rate", 0.7))</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>def softmax(values):</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">    shifted = values - values.max()</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">    exps = np.exp(shifted)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">    return exps / exps.sum()</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>target_index = vocab.index(target_token)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>logits = x @ W + b</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>probabilities = softmax(logits)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>one_hot = np.zeros(len(vocab))</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>one_hot[target_index] = 1.0</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>loss = -np.log(probabilities[target_index])</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" t="inlineStr"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>dlogit = probabilities - one_hot</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>dW = np.outer(x, dlogit)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>db = dlogit.copy()</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>dx = dlogit @ W.T</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>updated_W = W - learning_rate * dW</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>updated_b = b - learning_rate * db</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>updated_logits = x @ updated_W + updated_b</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>updated_probabilities = softmax(updated_logits)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>updated_loss = -np.log(updated_probabilities[target_index])</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" t="inlineStr"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>forward_df = pd.DataFrame({</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t xml:space="preserve">    "candidate_token": vocab,</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_before": np.round(logits, 4),</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_before": np.round(probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">    "is_target": one_hot.astype(int),</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t xml:space="preserve">    "dLoss_dlogit": np.round(dlogit, 4),</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>})</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>dW_df = pd.DataFrame(dW, columns=[f"dW_to_{token}" for token in vocab])</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>dW_df.insert(0, "input_feature", features)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>dW_df.iloc[:, 1:] = dW_df.iloc[:, 1:].round(4)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" t="inlineStr"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>dx_df = pd.DataFrame({</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t xml:space="preserve">    "input_feature": features,</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t xml:space="preserve">    "x_value": x,</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t xml:space="preserve">    "dLoss_dx": np.round(dx, 4),</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>})</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>update_df = pd.DataFrame({</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t xml:space="preserve">    "candidate_token": vocab,</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_before": np.round(logits, 4),</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_before": np.round(probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t xml:space="preserve">    "logit_after": np.round(updated_logits, 4),</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_after": np.round(updated_probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t xml:space="preserve">    "probability_change": np.round(updated_probabilities - probabilities, 4),</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>})</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" t="inlineStr"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>summary_df = pd.DataFrame([</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"state": "before", "target_token": target_token, "target_probability": round(float(probabilities[target_index]), 4), "loss": round(float(loss), 4)},</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"state": "after one step", "target_token": target_token, "target_probability": round(float(updated_probabilities[target_index]), 4), "loss": round(float(updated_loss), 4)},</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>])</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" t="inlineStr"/>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>chain_rule_df = pd.DataFrame([</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"step": 1, "gradient": "dLoss/dlogit", "formula": "probability - target", "meaning": "出力側のズレ"},</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"step": 2, "gradient": "dLoss/dW", "formula": "x outer dlogit", "meaning": "重みごとの責任"},</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"step": 3, "gradient": "dLoss/db", "formula": "dlogit", "meaning": "biasの責任"},</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"step": 4, "gradient": "dLoss/dx", "formula": "dlogit @ W.T", "meaning": "前段へ戻る信号"},</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"step": 5, "gradient": "update", "formula": "W - lr * dW", "meaning": "Lossを下げる向き"},</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>])</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" t="inlineStr"/>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t># Python in Excelで最後に表示したい表を選びます。</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>result_df = forward_df</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t># result_df = dW_df</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t># result_df = dx_df</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t># result_df = update_df</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t># result_df = summary_df</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t># result_df = chain_rule_df</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="3" t="inlineStr"/>
-    </row>
-    <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>result_df</t>
         </is>

--- a/第9回_Backpropagation/excel_backpropagation_demo.xlsx
+++ b/第9回_Backpropagation/excel_backpropagation_demo.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -166,6 +166,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,7 +695,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>よくある確認点</t>
         </is>
@@ -805,7 +811,7 @@
       <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>全10回ロードマップ</t>
         </is>
@@ -1059,7 +1065,7 @@
       <c r="J2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>第8回のLossとgradientを受けて、ズレを重みWと入力xへ戻す入口を確認します。</t>
         </is>
@@ -1087,7 +1093,7 @@
       <c r="J4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>入力ベクトルxと重みW</t>
         </is>
@@ -1241,7 +1247,7 @@
       <c r="J11" s="3" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>biasと学習設定</t>
         </is>
@@ -1408,7 +1414,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>まず前向き計算でlogit、probability、target、Lossへの入口を作ります。</t>
         </is>
@@ -1434,7 +1440,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>forward and output gradient</t>
         </is>
@@ -1628,7 +1634,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Softmax + Cross Entropyでは、出力側のgradientを probability - target と読めます。</t>
         </is>
@@ -1654,7 +1660,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>dLoss/dlogit</t>
         </is>
@@ -1836,7 +1842,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>dWは入力xとdlogitの掛け算、dxは前段へ戻るgradientです。</t>
         </is>
@@ -1862,7 +1868,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>dLoss/dW</t>
         </is>
@@ -1988,7 +1994,7 @@
       <c r="I10" s="3" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>dLoss/dx</t>
         </is>
@@ -2140,7 +2146,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Wとbiasを1ステップ更新し、正解tokenの確率が上がりLossが下がることを確認します。</t>
         </is>
@@ -2166,7 +2172,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>更新前後の比較</t>
         </is>
@@ -2338,7 +2344,7 @@
       <c r="I12" s="3" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Loss summary</t>
         </is>
@@ -2483,7 +2489,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>chain ruleは、後ろで出たズレを、式のつながりに沿って前へ戻す読み方です。</t>
         </is>
@@ -2509,7 +2515,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Backpropagationの小さな流れ</t>
         </is>
@@ -2733,7 +2739,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>実行手順</t>
         </is>
@@ -2827,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A91"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -2867,9 +2873,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6" ht="24" customHeight="1"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -2884,9 +2888,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9" ht="24" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -2950,9 +2952,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19" ht="24" customHeight="1"/>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2981,9 +2981,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" t="inlineStr"/>
-    </row>
+    <row r="24" ht="24" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
@@ -3026,9 +3024,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" t="inlineStr"/>
-    </row>
+    <row r="31" ht="24" customHeight="1"/>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
@@ -3057,9 +3053,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" t="inlineStr"/>
-    </row>
+    <row r="36" ht="24" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
@@ -3095,9 +3089,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" t="inlineStr"/>
-    </row>
+    <row r="42" ht="24" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
@@ -3147,9 +3139,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" t="inlineStr"/>
-    </row>
+    <row r="50" ht="24" customHeight="1"/>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
@@ -3171,9 +3161,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" t="inlineStr"/>
-    </row>
+    <row r="54" ht="24" customHeight="1"/>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
@@ -3209,9 +3197,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" t="inlineStr"/>
-    </row>
+    <row r="60" ht="24" customHeight="1"/>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
@@ -3268,9 +3254,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" t="inlineStr"/>
-    </row>
+    <row r="69" ht="24" customHeight="1"/>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
@@ -3299,9 +3283,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" t="inlineStr"/>
-    </row>
+    <row r="74" ht="24" customHeight="1"/>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
@@ -3351,9 +3333,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" t="inlineStr"/>
-    </row>
+    <row r="82" ht="24" customHeight="1"/>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
@@ -3403,9 +3383,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-    </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
